--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260929.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260929.xlsx
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>117,699,000</t>
+          <t>119,660,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>119,660,000</t>
+          <t>117,699,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>30,838,800</t>
+          <t>29,362,899</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>29,362,899</t>
+          <t>30,838,800</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
